--- a/output/stock_quant_scores/NVDA_info.xlsx
+++ b/output/stock_quant_scores/NVDA_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FW2"/>
+  <dimension ref="A1:GA2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1086,235 +1086,255 @@
       </c>
       <c r="EC1" s="1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketTime</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EF1" s="1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketPrice</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChange</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
+        <is>
+          <t>dividendDate</t>
+        </is>
+      </c>
+      <c r="FN1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="FO1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="FP1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="FQ1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="FR1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="FS1" s="1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="FT1" s="1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="FU1" s="1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="FV1" s="1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="FW1" s="1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="FX1" s="1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="FY1" s="1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>dividendDate</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FN1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FO1" s="1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="FP1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="FQ1" s="1" t="inlineStr">
-        <is>
-          <t>averageAnalystRating</t>
-        </is>
-      </c>
-      <c r="FR1" s="1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="FS1" s="1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="FT1" s="1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="FU1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="FV1" s="1" t="inlineStr">
+      <c r="FZ1" s="1" t="inlineStr">
         <is>
           <t>displayName</t>
         </is>
       </c>
-      <c r="FW1" s="1" t="inlineStr">
+      <c r="GA1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1440,28 +1460,28 @@
         <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>178.43</v>
+        <v>177.69</v>
       </c>
       <c r="AD2" t="n">
-        <v>179.72</v>
+        <v>178.17</v>
       </c>
       <c r="AE2" t="n">
-        <v>175.4</v>
+        <v>174.93</v>
       </c>
       <c r="AF2" t="n">
-        <v>179.78</v>
+        <v>179.77</v>
       </c>
       <c r="AG2" t="n">
-        <v>178.43</v>
+        <v>177.69</v>
       </c>
       <c r="AH2" t="n">
-        <v>179.72</v>
+        <v>178.17</v>
       </c>
       <c r="AI2" t="n">
-        <v>175.4</v>
+        <v>174.93</v>
       </c>
       <c r="AJ2" t="n">
-        <v>179.78</v>
+        <v>179.77</v>
       </c>
       <c r="AK2" t="n">
         <v>0.04</v>
@@ -1482,31 +1502,31 @@
         <v>2.102</v>
       </c>
       <c r="AQ2" t="n">
-        <v>50.321026</v>
+        <v>50.766384</v>
       </c>
       <c r="AR2" t="n">
-        <v>42.99272</v>
+        <v>43.25</v>
       </c>
       <c r="AS2" t="n">
-        <v>109731405</v>
+        <v>148071154</v>
       </c>
       <c r="AT2" t="n">
-        <v>109729964</v>
+        <v>148071154</v>
       </c>
       <c r="AU2" t="n">
-        <v>176300733</v>
+        <v>172388247</v>
       </c>
       <c r="AV2" t="n">
-        <v>189312480</v>
+        <v>187424260</v>
       </c>
       <c r="AW2" t="n">
-        <v>189312480</v>
+        <v>187424260</v>
       </c>
       <c r="AX2" t="n">
-        <v>176.83</v>
+        <v>169.25</v>
       </c>
       <c r="AY2" t="n">
-        <v>177.45</v>
+        <v>180</v>
       </c>
       <c r="AZ2" t="n">
         <v>1</v>
@@ -1515,7 +1535,7 @@
         <v>1</v>
       </c>
       <c r="BB2" t="n">
-        <v>4312584421376</v>
+        <v>4338392236032</v>
       </c>
       <c r="BC2" t="n">
         <v>86.62</v>
@@ -1530,19 +1550,19 @@
         <v>0.033333</v>
       </c>
       <c r="BG2" t="n">
-        <v>26.10174</v>
+        <v>26.258595</v>
       </c>
       <c r="BH2" t="n">
-        <v>176.207</v>
+        <v>176.5626</v>
       </c>
       <c r="BI2" t="n">
-        <v>141.32076</v>
+        <v>141.8218</v>
       </c>
       <c r="BJ2" t="n">
         <v>0.04</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.00022417755</v>
+        <v>0.00022511114</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
@@ -1553,43 +1573,43 @@
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>4289655996416</v>
+        <v>4283824078848</v>
       </c>
       <c r="BO2" t="n">
         <v>0.5241400000000001</v>
       </c>
       <c r="BP2" t="n">
-        <v>23325084000</v>
+        <v>23325813000</v>
       </c>
       <c r="BQ2" t="n">
         <v>24347000000</v>
       </c>
       <c r="BR2" t="n">
-        <v>196695074</v>
+        <v>217485473</v>
       </c>
       <c r="BS2" t="n">
-        <v>192121364</v>
+        <v>205241302</v>
       </c>
       <c r="BT2" t="n">
-        <v>1753920000</v>
+        <v>1755216000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1756425600</v>
+        <v>1757894400</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.0081</v>
+        <v>0.0089</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.04329</v>
+        <v>0.04328</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.68974996</v>
+        <v>0.6898</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="CA2" t="n">
         <v>25053817576</v>
@@ -1598,7 +1618,7 @@
         <v>4.113</v>
       </c>
       <c r="CC2" t="n">
-        <v>43.06589</v>
+        <v>43.32361</v>
       </c>
       <c r="CD2" t="n">
         <v>1737849600</v>
@@ -1616,7 +1636,7 @@
         <v>86597001216</v>
       </c>
       <c r="CI2" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CJ2" t="n">
         <v>4.12</v>
@@ -1630,16 +1650,16 @@
         <v>1717977600</v>
       </c>
       <c r="CM2" t="n">
-        <v>25.964</v>
+        <v>25.928</v>
       </c>
       <c r="CN2" t="n">
-        <v>43.647</v>
+        <v>43.588</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.4446603</v>
+        <v>0.467309</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CQ2" t="n">
         <v>0.01</v>
@@ -1653,7 +1673,7 @@
         </is>
       </c>
       <c r="CT2" t="n">
-        <v>177.1256</v>
+        <v>178.19</v>
       </c>
       <c r="CU2" t="n">
         <v>270</v>
@@ -1662,13 +1682,13 @@
         <v>100</v>
       </c>
       <c r="CW2" t="n">
-        <v>212.46928</v>
+        <v>213.45143</v>
       </c>
       <c r="CX2" t="n">
-        <v>210.5</v>
+        <v>211</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.34921</v>
+        <v>1.35938</v>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
@@ -1775,172 +1795,184 @@
       </c>
       <c r="EC2" t="inlineStr">
         <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="ED2" t="b">
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="ED2" t="n">
+        <v>1758931199</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>1758916801</v>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EG2" t="n">
+        <v>0.281389</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>178.19</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>NMS</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>finmb_32307</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>America/New_York</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>EDT</t>
+        </is>
+      </c>
+      <c r="EM2" t="n">
+        <v>-14400000</v>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>us_market</t>
+        </is>
+      </c>
+      <c r="EO2" t="b">
         <v>0</v>
       </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>NMS</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>finmb_32307</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>America/New_York</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>EDT</t>
-        </is>
-      </c>
-      <c r="EI2" t="n">
-        <v>-14400000</v>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>us_market</t>
-        </is>
-      </c>
-      <c r="EK2" t="b">
+      <c r="EP2" t="n">
+        <v>1.6273956</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>0.009217102</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>36.36821</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>0.256436</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EU2" t="n">
         <v>0</v>
       </c>
-      <c r="EL2" t="n">
-        <v>-0.7285701999999999</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>177.13</v>
-      </c>
-      <c r="EN2" t="inlineStr">
+      <c r="EV2" t="inlineStr">
+        <is>
+          <t>1.4 - Strong Buy</t>
+        </is>
+      </c>
+      <c r="EW2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EX2" t="b">
+        <v>1</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>917015400000</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>-0.3093375</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>177.6388</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>-0.5512085</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="FD2" t="inlineStr">
+        <is>
+          <t>174.93 - 179.77</t>
+        </is>
+      </c>
+      <c r="FE2" t="inlineStr">
+        <is>
+          <t>NasdaqGS</t>
+        </is>
+      </c>
+      <c r="FF2" t="n">
+        <v>172388247</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>1.0571461</v>
+      </c>
+      <c r="FI2" t="inlineStr">
+        <is>
+          <t>86.62 - 184.55</t>
+        </is>
+      </c>
+      <c r="FJ2" t="n">
+        <v>-6.3600006</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>-0.03446221</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>46.7309</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>1759363200</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>1763582400</v>
+      </c>
+      <c r="FO2" t="n">
+        <v>1763582400</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>1763582400</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>1756328400</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>1756328400</v>
+      </c>
+      <c r="FS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FT2" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="FU2" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="FV2" t="n">
+        <v>4.49903</v>
+      </c>
+      <c r="FW2" t="n">
+        <v>39.606316</v>
+      </c>
+      <c r="FX2" t="inlineStr">
         <is>
           <t>NVIDIA Corporation</t>
         </is>
       </c>
-      <c r="EO2" t="inlineStr">
+      <c r="FY2" t="inlineStr">
         <is>
           <t>NVIDIA Corporation</t>
         </is>
       </c>
-      <c r="EP2" t="n">
-        <v>-1.2999878</v>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>175.4 - 179.78</t>
-        </is>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>NasdaqGS</t>
-        </is>
-      </c>
-      <c r="ES2" t="n">
-        <v>176300733</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>90.51000000000001</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>1.0449088</v>
-      </c>
-      <c r="EV2" t="inlineStr">
-        <is>
-          <t>86.62 - 184.55</t>
-        </is>
-      </c>
-      <c r="EW2" t="n">
-        <v>-7.419998</v>
-      </c>
-      <c r="EX2" t="n">
-        <v>-0.040205896</v>
-      </c>
-      <c r="EY2" t="n">
-        <v>44.46603</v>
-      </c>
-      <c r="EZ2" t="n">
-        <v>1759363200</v>
-      </c>
-      <c r="FA2" t="n">
-        <v>1763582400</v>
-      </c>
-      <c r="FB2" t="n">
-        <v>1763582400</v>
-      </c>
-      <c r="FC2" t="n">
-        <v>1763582400</v>
-      </c>
-      <c r="FD2" t="n">
-        <v>1756328400</v>
-      </c>
-      <c r="FE2" t="n">
-        <v>1756328400</v>
-      </c>
-      <c r="FF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FG2" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="FH2" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="FI2" t="n">
-        <v>4.49799</v>
-      </c>
-      <c r="FJ2" t="n">
-        <v>39.37981</v>
-      </c>
-      <c r="FK2" t="n">
-        <v>0.92300415</v>
-      </c>
-      <c r="FL2" t="n">
-        <v>0.005238181</v>
-      </c>
-      <c r="FM2" t="n">
-        <v>35.80925</v>
-      </c>
-      <c r="FN2" t="n">
-        <v>0.2533899</v>
-      </c>
-      <c r="FO2" t="n">
-        <v>15</v>
-      </c>
-      <c r="FP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="FQ2" t="inlineStr">
-        <is>
-          <t>1.3 - Strong Buy</t>
-        </is>
-      </c>
-      <c r="FR2" t="b">
-        <v>1</v>
-      </c>
-      <c r="FS2" t="n">
-        <v>917015400000</v>
-      </c>
-      <c r="FT2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="FU2" t="n">
-        <v>1758740012</v>
-      </c>
-      <c r="FV2" t="inlineStr">
+      <c r="FZ2" t="inlineStr">
         <is>
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="FW2" t="n">
-        <v>1.3274</v>
+      <c r="GA2" t="n">
+        <v>1.3256</v>
       </c>
     </row>
   </sheetData>
